--- a/Document/데이터/LUNA_Narrative.xlsx
+++ b/Document/데이터/LUNA_Narrative.xlsx
@@ -46,7 +46,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Days'!$A$1:$H$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'RegularSlots'!$A$1:$J$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Spots'!$A$1:$D$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'InteractPoints'!$A$1:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'InteractPoints'!$A$1:$J$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Scenes'!$A$1:$I$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Steps'!$A$1:$K$819</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Choices'!$A$1:$H$11</definedName>
@@ -507,29 +507,41 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>언제 나타나는지 — commute_in(출근길)/commute_out(퇴근길)/both
+        <t>이 지점에 서 있는 캐릭터(Characters.id). 빈값 = 사물·전단 등. 같은 actor를 phase·when이 다른 지점 여러 개에 두면 시간대별 위치 이동 표현
 💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>나타날 조건(when 문법). 예: day == 2 → 2일차에만 등장
+        <t>언제 나타나는지 — commute_in(출근길)/commute_out(퇴근길)/both
 💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>조사했을 때 재생할 씬 id. 'group:이름'이면 그 그룹의 씬들 중 selection 규칙대로 고른다. 'shop:'이면 상점
+        <t>대사 시작 방식 — interact(E키 상호작용, 기본)/proximity(재생 범위 진입 시 자동 재생 — E 아이콘 없음·조작 락 없음·street_auto_next_delay_sec 간격 자동 진행. 현재 실사용 0 = 예약)
 💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
+        <t>나타날 조건(when 문법). 예: day == 2 → 2일차에만 등장
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>조사했을 때 재생할 씬 id. 'group:이름'이면 그 그룹의 씬들 중 selection 규칙대로 고른다. 'shop:'이면 상점
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
         <t>반복 규칙 — once(한 번만)/repeat(계속)/sequential(볼 때마다 다음 씬)/conditional(조건 맞는 첫 씬). 시바견처럼 '첫 대화 후 반복 대사'는 conditional
 💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>작업 메모
 💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
@@ -1187,7 +1199,7 @@
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>timeline(Unity 타임라인 — 주력) 또는 gif(스파인 애니를 GIF로 뽑은 것)
+        <t>timeline(Unity 타임라인 — 주력) / gif(스파인 애니를 GIF로 뽑은 것) / sprite(포스터 뷰 — 이미지 1장을 화면 중앙에 띄우고 timeline 스텝의 text가 하단 대사. 현재 실사용 0 = 예약)
 💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
       </text>
     </comment>
@@ -3265,17 +3277,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="47" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3296,25 +3310,35 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
+          <t>actor</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
           <t>phase</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>when</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>scene_or_shop</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>selection</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -3336,27 +3360,33 @@
           <t>object</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
         <is>
           <t>commute_in</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>interact</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>day == 2</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>d2_news</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>once</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>전광판 뉴스(세계관 떡밥)</t>
         </is>
@@ -3378,27 +3408,33 @@
           <t>object</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr"/>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>commute_in</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>interact</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>day == 3</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>d3_news</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>once</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>전광판 뉴스(벡터 정화사업)</t>
         </is>
@@ -3422,25 +3458,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>commute_in</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>interact</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>day == 2 &amp;&amp; !flag.q_lost_box_started</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>d2_vendor_intro</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>once</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>노점상 완 첫 인사 + 퀘스트 시작</t>
         </is>
@@ -3464,25 +3510,35 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
           <t>both</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>interact</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>day &gt;= 3</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>shop:vendor</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>repeat</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>노점 상점(과일·믹서 구매)</t>
         </is>
@@ -3504,27 +3560,33 @@
           <t>object</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
         <is>
           <t>commute_out</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>interact</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>flag.q_lost_box_started &amp;&amp; !flag.q_lost_box_done</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>d2_box_found</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>once</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>잃어버린 상자(퀘스트)</t>
         </is>
@@ -3546,27 +3608,33 @@
           <t>object</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>commute_in</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>interact</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>day == 3 &amp;&amp; !flag.d3_cat_seen</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>d3_alley_cat</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>once</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>노란 꼬리 목격 → d3 아일리 선택지 연동</t>
         </is>
@@ -3590,25 +3658,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>shiba</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>both</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>interact</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>day &gt;= 2</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>group:np_shiba</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>시바견 NPC — 구엔진 shiba.json 이식 (첫 조우→반복)</t>
         </is>
@@ -3630,27 +3708,33 @@
           <t>object</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>interact</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>day &gt;= 2</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>group:ob_parttime</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>sequential</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>[이식] parttime_posting — 볼 때마다 다음 감상(순차 소비 데모)</t>
         </is>
@@ -3672,27 +3756,33 @@
           <t>object</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>interact</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>day &gt;= 2</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>group:ob_vending</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>[이식] vending_machine — 골드에 따라 분기(조건 선택 데모)</t>
         </is>
@@ -3714,27 +3804,33 @@
           <t>object</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>commute_out</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>interact</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>day &gt;= 2</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>group:ob_experiment</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>once</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>[이식] experiment_recruit — 코라테크 임상시험(세계관 복선)</t>
         </is>
@@ -3756,34 +3852,40 @@
           <t>object</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
         <is>
           <t>commute_out</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>interact</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>day &gt;= 2 &amp;&amp; flag.q_lost_box_done</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>group:ob_toilet</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>once</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>[이식] toilet_bin — 유머</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H12"/>
+  <autoFilter ref="A1:J12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -44947,17 +45049,17 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>(미확인)</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>미사용</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Addressable에 luna 폴더 없음 — character_anim.json의 luna 클립 실물 위치 확인 필요</t>
+          <t>바 내부는 1인칭 — 루나는 초상·스탠딩 없이 이름+대사만 출력. character_anim의 luna 항목은 예약</t>
         </is>
       </c>
     </row>

--- a/Document/데이터/LUNA_Narrative.xlsx
+++ b/Document/데이터/LUNA_Narrative.xlsx
@@ -2,31 +2,31 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INFO" sheetId="1" r:id="R6900c7a9366b4e91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Characters" sheetId="2" r:id="Rd2e95e89253b4988"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expressions" sheetId="3" r:id="R1c2e828e5d3b46d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExpressionParts" sheetId="4" r:id="R0785ee6216e74cb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cutscenes" sheetId="5" r:id="Ra422359969694259"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResourceMap" sheetId="6" r:id="R624e301f28194e29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldAnims" sheetId="7" r:id="R8d2029fcba274a3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Barks" sheetId="8" r:id="R9f3279166c324467"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tastes" sheetId="9" r:id="R98d921aeeab54703"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dossier" sheetId="10" r:id="R45396744ecdc4738"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Days" sheetId="11" r:id="R3af16f3fc10444c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RegularSlots" sheetId="12" r:id="R12831faa153645a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spots" sheetId="13" r:id="R62c8fecba9844feb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InteractPoints" sheetId="14" r:id="R2716bc1fc1d74e89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenes" sheetId="15" r:id="R514fcc38b7c74330"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steps" sheetId="16" r:id="Rea8b3af8fc25429a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choices" sheetId="17" r:id="R20b1400533d648e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OrderRules" sheetId="18" r:id="R1719d8ca289a4621"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quests" sheetId="19" r:id="R9cac039107c64455"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QuestStages" sheetId="20" r:id="R4d3d063ca5714b18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endings" sheetId="21" r:id="Re7364964b1e5442f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AffinityMatrix" sheetId="22" r:id="R6be2765806ae4960"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UIStrings" sheetId="23" r:id="R6a8c103499f54ecb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TextTags" sheetId="24" r:id="R759785167c5e4ce9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BarkSituations" sheetId="25" r:id="Rb06339bba42e47b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INFO" sheetId="1" r:id="Rfb9ab0a5418c4fe0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Characters" sheetId="2" r:id="Re253fcbfa3004425"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expressions" sheetId="3" r:id="Ra0c91d67da814876"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExpressionParts" sheetId="4" r:id="R65e1616c5ee54392"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cutscenes" sheetId="5" r:id="R02afcf59c1c043db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResourceMap" sheetId="6" r:id="R80d92b44360544a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldAnims" sheetId="7" r:id="R0cc8fb3ba5414721"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Barks" sheetId="8" r:id="R0a509682800b4504"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tastes" sheetId="9" r:id="Re9a643140ddc46d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dossier" sheetId="10" r:id="R917cb61a96e64c68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Days" sheetId="11" r:id="R01b76145eb52437b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RegularSlots" sheetId="12" r:id="Rc94bea12e638439c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spots" sheetId="13" r:id="R9ab5fdd9685d4199"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InteractPoints" sheetId="14" r:id="Rf2a2e966f9784ac3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenes" sheetId="15" r:id="Rda1daea958494d33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steps" sheetId="16" r:id="Rfe85c79cc76148e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choices" sheetId="17" r:id="R70def33c269742f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OrderRules" sheetId="18" r:id="Rf5ed6c08877b42ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quests" sheetId="19" r:id="R9d0059081d334483"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QuestStages" sheetId="20" r:id="R13abbefced414b75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endings" sheetId="21" r:id="R7a808ed1d2c942e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AffinityMatrix" sheetId="22" r:id="R712d7cc8db954626"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UIStrings" sheetId="23" r:id="R8efaa5067ea64195"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TextTags" sheetId="24" r:id="R07c5a20468ce489a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BarkSituations" sheetId="25" r:id="R9bc3f2d0b42f4d92"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3160,7 +3160,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76e4dfd97530460d"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2a8355d7e604229"/>
 </x:worksheet>
 </file>
 
@@ -3377,7 +3377,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdddf4352e2a7466b"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b1818d09ecf4b13"/>
 </x:worksheet>
 </file>
 
@@ -3498,7 +3498,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd76806dabec84439"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23708226507e46c2"/>
 </x:worksheet>
 </file>
 
@@ -3715,7 +3715,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d46e1c0946340a0"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4de6925437142b0"/>
 </x:worksheet>
 </file>
 
@@ -4104,7 +4104,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4440c705631646d6"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbee855d15ab64025"/>
 </x:worksheet>
 </file>
 
@@ -6556,7 +6556,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b91009a4979435c"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14b8ed80554041ff"/>
 </x:worksheet>
 </file>
 
@@ -59029,7 +59029,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac25e69a46f04d44"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ad149a459024c19"/>
 </x:worksheet>
 </file>
 
@@ -60912,7 +60912,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6de000c71cd4a20"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69fd9aad627b4d01"/>
 </x:worksheet>
 </file>
 
@@ -61103,7 +61103,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc41077d6c1f4bb3"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R577fb2a8a1034647"/>
 </x:worksheet>
 </file>
 
@@ -61156,7 +61156,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb635c77c70442d9"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fb1c45833604727"/>
 </x:worksheet>
 </file>
 
@@ -62391,7 +62391,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fcb5534db9f4f9f"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb166fe20c1ea43a0"/>
 </x:worksheet>
 </file>
 
@@ -62438,7 +62438,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53716eef2fc4423e"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8bd7ca191454811"/>
 </x:worksheet>
 </file>
 
@@ -62608,7 +62608,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcca14280fabb47db"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5a12c9fd7ad45e9"/>
 </x:worksheet>
 </file>
 
@@ -62771,7 +62771,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ab08f2e2b064b24"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3eb4e135d45e40d8"/>
 </x:worksheet>
 </file>
 
@@ -62782,7 +62782,7 @@
   </x:sheetPr>
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" customWidth="1"/>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="32" customWidth="1"/>
     <x:col min="3" max="3" width="60" customWidth="1"/>
   </x:cols>
@@ -63370,9 +63370,86 @@
         <x:v>Manual saving is only available at home.</x:v>
       </x:c>
     </x:row>
+    <x:row r="54" ht="15" hidden="0" customHeight="1">
+      <x:c r="A54" t="str">
+        <x:v>ui_home_exit</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>밖으로 나간다</x:v>
+      </x:c>
+      <x:c r="C54" t="str">
+        <x:v>Go Outside</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="15" hidden="0" customHeight="1">
+      <x:c r="A55" t="str">
+        <x:v>ui_home_exit_blocked</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>지금은 집을 나갈 수 없습니다.</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>You cannot leave home right now.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="15" hidden="0" customHeight="1">
+      <x:c r="A56" t="str">
+        <x:v>ui_home_sleep_confirm</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>하루를 종료하시겠습니까?</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>End the day?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="15" hidden="0" customHeight="1">
+      <x:c r="A57" t="str">
+        <x:v>ui_save_overwrite_confirm</x:v>
+      </x:c>
+      <x:c r="B57" t="str">
+        <x:v>이 슬롯에 덮어쓰시겠습니까?</x:v>
+      </x:c>
+      <x:c r="C57" t="str">
+        <x:v>Overwrite this save slot?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="15" hidden="0" customHeight="1">
+      <x:c r="A58" t="str">
+        <x:v>ui_save_success</x:v>
+      </x:c>
+      <x:c r="B58" t="str">
+        <x:v>저장되었습니다.</x:v>
+      </x:c>
+      <x:c r="C58" t="str">
+        <x:v>Game saved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="15" hidden="0" customHeight="1">
+      <x:c r="A59" t="str">
+        <x:v>ui_autosave_failed</x:v>
+      </x:c>
+      <x:c r="B59" t="str">
+        <x:v>자동 저장에 실패했습니다. 이전 자동 저장은 유지됩니다.</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>Autosave failed. Your previous autosave has been preserved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="15" hidden="0" customHeight="1">
+      <x:c r="A60" t="str">
+        <x:v>ui_home_map_transition_failed</x:v>
+      </x:c>
+      <x:c r="B60" t="str">
+        <x:v>이동하지 못했습니다. 잠시 후 다시 시도해 주세요.</x:v>
+      </x:c>
+      <x:c r="C60" t="str">
+        <x:v>Unable to move to the next area. Please try again.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d58ae5b1fe44374"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5a32da4cd744d68"/>
 </x:worksheet>
 </file>
 
@@ -63559,7 +63636,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R806706ca90254e9c"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf60538a67d74d57"/>
 </x:worksheet>
 </file>
 
@@ -64002,7 +64079,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd27d3f1445e044ca"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdaa2cd79eb2428a"/>
 </x:worksheet>
 </file>
 
@@ -65102,7 +65179,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdaa2bffbce54456"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R146e75ee20d447b6"/>
 </x:worksheet>
 </file>
 
@@ -66418,7 +66495,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20322db076c3408a"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2bbb9c124944bed"/>
 </x:worksheet>
 </file>
 
@@ -66965,7 +67042,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b46b2c1b8ba4488"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5264a2ba9ed34995"/>
 </x:worksheet>
 </file>
 
@@ -67468,7 +67545,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a0420fb4407458b"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf46de37ac424772"/>
 </x:worksheet>
 </file>
 
@@ -68001,7 +68078,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4774863d16c489b"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R571c9f1d118342b3"/>
 </x:worksheet>
 </file>
 
@@ -73124,7 +73201,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f20256495c047d8"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51a212f426a148fe"/>
 </x:worksheet>
 </file>
 
@@ -73419,6 +73496,6 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97d368d8c81441e9"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2b9df269fa14b9e"/>
 </x:worksheet>
 </file>